--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/08 Agosto/Liquidacióncvs -agosto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1053" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D89419FB-4088-495F-A354-8A99D3BF3052}"/>
+  <xr:revisionPtr revIDLastSave="1062" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7D2DF8D-A887-45DD-BFE0-595D1939A7F5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="38">
   <si>
     <t>BARBOSA</t>
   </si>
@@ -150,6 +150,9 @@
   </si>
   <si>
     <t>ACCESORIOS</t>
+  </si>
+  <si>
+    <t>METRO EST. SAN ANTONIO</t>
   </si>
 </sst>
 </file>
@@ -536,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}">
-  <dimension ref="A1:E151"/>
+  <dimension ref="A1:E157"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -3112,6 +3115,108 @@
         <v>54450</v>
       </c>
     </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>35</v>
+      </c>
+      <c r="B152" t="s">
+        <v>37</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D152" s="2">
+        <v>0</v>
+      </c>
+      <c r="E152" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>35</v>
+      </c>
+      <c r="B153" t="s">
+        <v>37</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D153" s="2">
+        <v>8</v>
+      </c>
+      <c r="E153" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>35</v>
+      </c>
+      <c r="B154" t="s">
+        <v>37</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D154" s="2">
+        <v>2</v>
+      </c>
+      <c r="E154" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>35</v>
+      </c>
+      <c r="B155" t="s">
+        <v>37</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D155" s="2">
+        <v>20</v>
+      </c>
+      <c r="E155" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>35</v>
+      </c>
+      <c r="B156" t="s">
+        <v>37</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D156" s="2">
+        <v>25</v>
+      </c>
+      <c r="E156" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>35</v>
+      </c>
+      <c r="B157" t="s">
+        <v>37</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D157" s="2">
+        <v>500000</v>
+      </c>
+      <c r="E157" s="2">
+        <v>1000</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E151" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/08 Agosto/Liquidacióncvs -agosto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1062" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7D2DF8D-A887-45DD-BFE0-595D1939A7F5}"/>
+  <xr:revisionPtr revIDLastSave="1069" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{024B314A-D039-463B-AA2D-2E6B9FB305E4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$E$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$E$155</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="38">
   <si>
     <t>BARBOSA</t>
   </si>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}">
-  <dimension ref="A1:E157"/>
+  <dimension ref="A1:E155"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -2695,33 +2695,33 @@
         <v>35</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D127" s="2">
-        <v>9000000</v>
+        <v>8000000</v>
       </c>
       <c r="E127" s="2">
-        <v>3000</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>35</v>
       </c>
-      <c r="B128" s="2" t="s">
-        <v>0</v>
+      <c r="B128" t="s">
+        <v>2</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D128" s="2">
-        <v>8000000</v>
+        <v>2500000</v>
       </c>
       <c r="E128" s="2">
-        <v>2400</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
@@ -2729,16 +2729,16 @@
         <v>35</v>
       </c>
       <c r="B129" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D129" s="2">
-        <v>2500000</v>
+        <v>5500000</v>
       </c>
       <c r="E129" s="2">
-        <v>1000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
@@ -2746,16 +2746,16 @@
         <v>35</v>
       </c>
       <c r="B130" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D130" s="2">
-        <v>5500000</v>
+        <v>3000000</v>
       </c>
       <c r="E130" s="2">
-        <v>1500</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
@@ -2763,16 +2763,16 @@
         <v>35</v>
       </c>
       <c r="B131" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D131" s="2">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="E131" s="2">
-        <v>1450</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
@@ -2780,16 +2780,16 @@
         <v>35</v>
       </c>
       <c r="B132" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D132" s="2">
-        <v>5000000</v>
+        <v>7500000</v>
       </c>
       <c r="E132" s="2">
-        <v>1500</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -2797,16 +2797,16 @@
         <v>35</v>
       </c>
       <c r="B133" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D133" s="2">
-        <v>7500000</v>
+        <v>8000000</v>
       </c>
       <c r="E133" s="2">
-        <v>3500</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
@@ -2814,16 +2814,16 @@
         <v>35</v>
       </c>
       <c r="B134" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D134" s="2">
-        <v>8000000</v>
+        <v>5500000</v>
       </c>
       <c r="E134" s="2">
-        <v>2400</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
@@ -2831,16 +2831,16 @@
         <v>35</v>
       </c>
       <c r="B135" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D135" s="2">
-        <v>5500000</v>
+        <v>2500000</v>
       </c>
       <c r="E135" s="2">
-        <v>2000</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
@@ -2848,16 +2848,16 @@
         <v>35</v>
       </c>
       <c r="B136" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D136" s="2">
-        <v>2500000</v>
+        <v>4000000</v>
       </c>
       <c r="E136" s="2">
-        <v>1200</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -2865,16 +2865,16 @@
         <v>35</v>
       </c>
       <c r="B137" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D137" s="2">
-        <v>4000000</v>
+        <v>2000000</v>
       </c>
       <c r="E137" s="2">
-        <v>2000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
@@ -2882,16 +2882,16 @@
         <v>35</v>
       </c>
       <c r="B138" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D138" s="2">
-        <v>2000000</v>
+        <v>5000000</v>
       </c>
       <c r="E138" s="2">
-        <v>1100</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
@@ -2899,16 +2899,16 @@
         <v>35</v>
       </c>
       <c r="B139" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D139" s="2">
-        <v>5000000</v>
+        <v>3000000</v>
       </c>
       <c r="E139" s="2">
-        <v>2200</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
@@ -2916,13 +2916,13 @@
         <v>35</v>
       </c>
       <c r="B140" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D140" s="2">
-        <v>3000000</v>
+        <v>6000000</v>
       </c>
       <c r="E140" s="2">
         <v>1800</v>
@@ -2933,16 +2933,16 @@
         <v>35</v>
       </c>
       <c r="B141" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D141" s="2">
-        <v>6000000</v>
+        <v>4000000</v>
       </c>
       <c r="E141" s="2">
-        <v>1800</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
@@ -2950,16 +2950,16 @@
         <v>35</v>
       </c>
       <c r="B142" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D142" s="2">
-        <v>4000000</v>
+        <v>4500000</v>
       </c>
       <c r="E142" s="2">
-        <v>2850</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
@@ -2967,16 +2967,16 @@
         <v>35</v>
       </c>
       <c r="B143" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D143" s="2">
-        <v>9500000</v>
+        <v>3000000</v>
       </c>
       <c r="E143" s="2">
-        <v>3700</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
@@ -2984,16 +2984,16 @@
         <v>35</v>
       </c>
       <c r="B144" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D144" s="2">
-        <v>4500000</v>
+        <v>7000000</v>
       </c>
       <c r="E144" s="2">
-        <v>3500</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
@@ -3001,16 +3001,16 @@
         <v>35</v>
       </c>
       <c r="B145" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D145" s="2">
-        <v>3000000</v>
+        <v>4000000</v>
       </c>
       <c r="E145" s="2">
-        <v>2500</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
@@ -3018,16 +3018,16 @@
         <v>35</v>
       </c>
       <c r="B146" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D146" s="2">
-        <v>7000000</v>
+        <v>5500000</v>
       </c>
       <c r="E146" s="2">
-        <v>6800</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
@@ -3035,16 +3035,16 @@
         <v>35</v>
       </c>
       <c r="B147" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D147" s="2">
-        <v>4000000</v>
+        <v>3000000</v>
       </c>
       <c r="E147" s="2">
-        <v>2600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
@@ -3052,16 +3052,16 @@
         <v>35</v>
       </c>
       <c r="B148" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D148" s="2">
-        <v>5500000</v>
+        <v>117000000</v>
       </c>
       <c r="E148" s="2">
-        <v>2650</v>
+        <v>54450</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
@@ -3069,16 +3069,16 @@
         <v>35</v>
       </c>
       <c r="B149" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D149" s="2">
-        <v>3000000</v>
+        <v>10000</v>
       </c>
       <c r="E149" s="2">
-        <v>1000</v>
+        <v>54450</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
@@ -3086,16 +3086,16 @@
         <v>35</v>
       </c>
       <c r="B150" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="D150" s="2">
-        <v>117000000</v>
+        <v>0</v>
       </c>
       <c r="E150" s="2">
-        <v>54450</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
@@ -3103,16 +3103,16 @@
         <v>35</v>
       </c>
       <c r="B151" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D151" s="2">
-        <v>117000000</v>
+        <v>8</v>
       </c>
       <c r="E151" s="2">
-        <v>54450</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
@@ -3123,10 +3123,10 @@
         <v>37</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D152" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E152" s="2">
         <v>1000</v>
@@ -3140,10 +3140,10 @@
         <v>37</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D153" s="2">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E153" s="2">
         <v>1000</v>
@@ -3157,10 +3157,10 @@
         <v>37</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D154" s="2">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E154" s="2">
         <v>1000</v>
@@ -3174,51 +3174,17 @@
         <v>37</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D155" s="2">
-        <v>20</v>
+        <v>100000</v>
       </c>
       <c r="E155" s="2">
         <v>1000</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
-        <v>35</v>
-      </c>
-      <c r="B156" t="s">
-        <v>37</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D156" s="2">
-        <v>25</v>
-      </c>
-      <c r="E156" s="2">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
-        <v>35</v>
-      </c>
-      <c r="B157" t="s">
-        <v>37</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D157" s="2">
-        <v>500000</v>
-      </c>
-      <c r="E157" s="2">
-        <v>1000</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E151" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
+  <autoFilter ref="A1:E155" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>